--- a/temple_excel/样例.xlsx
+++ b/temple_excel/样例.xlsx
@@ -515,11 +515,11 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>彰武</t>
+          <t>王二</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>[{'level': 'info', 'msg': '右边成绩有效 总有效成绩：1 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：3 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：4 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：5 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：6 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：7 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：8 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：9 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：10 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：11 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：12 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：13 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：14 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：15 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：16 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：17 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：18 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：19 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：20 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：21 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：22 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：23 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：24 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：25 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：26 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：27 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：28 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：29 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：30 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：31 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：32 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：33 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：34 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：35 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：36 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：37 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：38 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：39 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：40 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：41 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：42 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：43 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：44 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：45 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：46 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：47 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：48 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：49 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：50 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：51 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：52 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：53 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：54 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：55 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：56 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：57 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：58 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：59 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：60 次'}]</t>
+          <t>[{'level': 'info', 'msg': '左边成绩有效 有效成绩：1 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：3 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：4 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：5 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：6 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：7 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：8 次'}, {'level': 'error', 'msg': '左边无效成绩，双脚经过次数 2'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：9 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：10 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：11 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：12 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：13 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：14 次'}, {'level': 'error', 'msg': '右边无效成绩，双脚经过次数 3'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：15 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：16 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：17 次'}, {'level': 'error', 'msg': '右边无效成绩，双脚经过次数 3'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：18 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：19 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：20 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：21 次'}, {'level': 'error', 'msg': '左边无效成绩，双脚经过次数 1'}]</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
@@ -559,11 +559,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>王二</t>
+          <t>彰武</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -580,18 +580,18 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>[{'level': 'info', 'msg': '右边成绩有效 总有效成绩：1 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：3 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：4 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：5 次'}]</t>
+          <t>[{'level': 'info', 'msg': '左边成绩有效 有效成绩：1 次'}, {'level': 'error', 'msg': '左边无效成绩，双脚经过次数 1'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：3 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：4 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：5 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：6 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：7 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：8 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：9 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：10 次'}]</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>5</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>

--- a/temple_excel/样例.xlsx
+++ b/temple_excel/样例.xlsx
@@ -515,11 +515,11 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>王二</t>
+          <t>彰武</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -536,18 +536,18 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>[{'level': 'info', 'msg': '左边成绩有效 有效成绩：1 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：3 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：4 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：5 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：6 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：7 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：8 次'}, {'level': 'error', 'msg': '左边无效成绩，双脚经过次数 2'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：9 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：10 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：11 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：12 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：13 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：14 次'}, {'level': 'error', 'msg': '右边无效成绩，双脚经过次数 3'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：15 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：16 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：17 次'}, {'level': 'error', 'msg': '右边无效成绩，双脚经过次数 3'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：18 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：19 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：20 次'}, {'level': 'warning', 'msg': '警报 右边没过线重复过左面'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：21 次'}, {'level': 'error', 'msg': '左边无效成绩，双脚经过次数 1'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
@@ -559,11 +559,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>彰武</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -580,18 +580,18 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>[{'level': 'info', 'msg': '左边成绩有效 有效成绩：1 次'}, {'level': 'error', 'msg': '左边无效成绩，双脚经过次数 1'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：3 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：4 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：5 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：6 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：7 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：8 次'}, {'level': 'info', 'msg': '左边成绩有效 有效成绩：9 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：10 次'}]</t>
+          <t>[{'level': 'info', 'msg': '右边成绩有效 总有效成绩：1 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：3 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：4 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：5 次'}]</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
@@ -602,12 +602,10 @@
           <t>女子组</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>段位</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -616,7 +614,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -631,7 +629,7 @@
         <v>5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
@@ -646,10 +644,12 @@
           <t>女子组</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>段位</t>
+          <t>王二</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -666,18 +666,18 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[{'level': 'info', 'msg': '右边成绩有效 总有效成绩：1 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：2 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：3 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：4 次'}, {'level': 'info', 'msg': '右边成绩有效 总有效成绩：5 次'}]</t>
+          <t>[{'level': 'info', 'msg': '右边成绩有效 总有效成绩：1 次'}]</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
